--- a/ChecklisteBewertungsschema/EvaluationHW.xlsx
+++ b/ChecklisteBewertungsschema/EvaluationHW.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bjarnejanssen/Documents/GitHub/Auto1/ChecklisteBewertungsschema/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bjarn\Documents\GitHub\Auto1\ChecklisteBewertungsschema\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{35D17B61-6EB8-974E-85E6-299E43633956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFCA51C9-8DC2-4223-BDA9-75BBE0A708BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="22680" windowHeight="15980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Report" sheetId="2" r:id="rId1"/>
@@ -134,7 +134,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="290">
   <si>
     <t>LaTeX</t>
   </si>
@@ -874,21 +874,6 @@
     <t>Parameter</t>
   </si>
   <si>
-    <t>Person 1</t>
-  </si>
-  <si>
-    <t>Person 2</t>
-  </si>
-  <si>
-    <t>Person 3</t>
-  </si>
-  <si>
-    <t>Person 4</t>
-  </si>
-  <si>
-    <t>Person 5</t>
-  </si>
-  <si>
     <t>Alle Personen</t>
   </si>
   <si>
@@ -974,6 +959,51 @@
   </si>
   <si>
     <t xml:space="preserve">halflydone </t>
+  </si>
+  <si>
+    <t>Bjarne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bjarne </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jenik </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jenik, Aiko </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sven </t>
+  </si>
+  <si>
+    <t xml:space="preserve">alle </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aiko </t>
+  </si>
+  <si>
+    <t>Sven</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jan, Sven </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jenik Kröger </t>
+  </si>
+  <si>
+    <t>Sven Hein</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jan Ahrens </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aiko Cassens </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bjarne Janssen </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sven, Jenik </t>
   </si>
 </sst>
 </file>
@@ -1207,6 +1237,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1224,9 +1257,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1514,45 +1544,45 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:M406"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:4" ht="34" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:4" ht="33.6" x14ac:dyDescent="0.65">
       <c r="A2" s="17" t="s">
         <v>39</v>
       </c>
       <c r="B2" s="17"/>
       <c r="C2" s="17"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="23" t="s">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="B7" s="23"/>
-      <c r="C7" s="23"/>
-    </row>
-    <row r="10" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="B7" s="24"/>
+      <c r="C7" s="24"/>
+    </row>
+    <row r="10" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>4</v>
       </c>
@@ -1566,25 +1596,25 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C14" s="3"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C15" s="3"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>84</v>
       </c>
@@ -1592,27 +1622,27 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B19" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>83</v>
       </c>
       <c r="B21" s="4"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>82</v>
       </c>
       <c r="B22" s="4"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>81</v>
       </c>
@@ -1620,7 +1650,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>7</v>
       </c>
@@ -1628,20 +1658,20 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="24" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A28" s="6" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="19" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ht="18" x14ac:dyDescent="0.35">
       <c r="A31" s="5" t="s">
         <v>78</v>
       </c>
       <c r="H31" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
         <v>79</v>
       </c>
@@ -1654,8 +1684,11 @@
       <c r="F32" s="8">
         <v>10</v>
       </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="G32" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="7"/>
       <c r="B33" s="8" t="s">
         <v>87</v>
@@ -1667,7 +1700,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="8"/>
       <c r="B34" s="8" t="s">
         <v>89</v>
@@ -1679,7 +1712,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="8"/>
       <c r="B35" s="8" t="s">
         <v>63</v>
@@ -1691,7 +1724,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="8"/>
       <c r="B36" s="8" t="s">
         <v>91</v>
@@ -1703,7 +1736,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="8"/>
       <c r="B37" s="8" t="s">
         <v>37</v>
@@ -1715,7 +1748,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="7"/>
       <c r="B38" s="8" t="s">
         <v>92</v>
@@ -1731,7 +1764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="7"/>
       <c r="B39" s="8"/>
       <c r="C39" s="8" t="s">
@@ -1743,7 +1776,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="8"/>
       <c r="B40" s="8"/>
       <c r="C40" s="8" t="s">
@@ -1755,7 +1788,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="8"/>
       <c r="B41" s="8"/>
       <c r="C41" s="8" t="s">
@@ -1769,7 +1802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="8"/>
       <c r="B42" s="8"/>
       <c r="C42" s="8" t="s">
@@ -1783,7 +1816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="8"/>
       <c r="B43" s="8"/>
       <c r="C43" s="8" t="s">
@@ -1795,7 +1828,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="8"/>
       <c r="B44" s="8"/>
       <c r="C44" s="8" t="s">
@@ -1807,7 +1840,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="8"/>
       <c r="B45" s="8"/>
       <c r="C45" s="8"/>
@@ -1820,7 +1853,7 @@
       </c>
       <c r="F45" s="8"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E46">
         <f>SUM(E32:E45)</f>
         <v>0</v>
@@ -1830,14 +1863,14 @@
         <v>90</v>
       </c>
     </row>
-    <row r="48" spans="1:12" s="5" customFormat="1" ht="19" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" s="5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A48" s="5" t="s">
         <v>64</v>
       </c>
       <c r="K48"/>
       <c r="L48"/>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" s="7" t="s">
         <v>64</v>
       </c>
@@ -1852,11 +1885,11 @@
       <c r="F49" s="8">
         <v>10</v>
       </c>
-      <c r="G49" s="24" t="s">
+      <c r="G49" s="25" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50" s="7"/>
       <c r="B50" s="7" t="s">
         <v>66</v>
@@ -1869,12 +1902,12 @@
       <c r="F50" s="8">
         <v>5</v>
       </c>
-      <c r="G50" s="24"/>
+      <c r="G50" s="25"/>
       <c r="H50" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51" s="7"/>
       <c r="B51" s="7"/>
       <c r="C51" s="8" t="s">
@@ -1885,9 +1918,9 @@
       <c r="F51" s="8">
         <v>5</v>
       </c>
-      <c r="G51" s="24"/>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="G51" s="25"/>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A52" s="7"/>
       <c r="B52" s="8"/>
       <c r="C52" s="8" t="s">
@@ -1898,12 +1931,12 @@
       <c r="F52" s="8">
         <v>5</v>
       </c>
-      <c r="G52" s="24"/>
+      <c r="G52" s="25"/>
       <c r="H52" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.2">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53" s="7"/>
       <c r="B53" s="7"/>
       <c r="C53" s="8" t="s">
@@ -1914,12 +1947,12 @@
       <c r="F53" s="8">
         <v>10</v>
       </c>
-      <c r="G53" s="24"/>
+      <c r="G53" s="25"/>
       <c r="H53" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54" s="8"/>
       <c r="B54" s="7"/>
       <c r="C54" s="8" t="s">
@@ -1930,12 +1963,12 @@
       <c r="F54" s="8">
         <v>25</v>
       </c>
-      <c r="G54" s="24"/>
-      <c r="H54" s="29">
+      <c r="G54" s="25"/>
+      <c r="H54" s="23">
         <v>0.9</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A55" s="7"/>
       <c r="B55" s="7"/>
       <c r="C55" s="8" t="s">
@@ -1946,12 +1979,12 @@
       <c r="F55" s="8">
         <v>5</v>
       </c>
-      <c r="G55" s="24"/>
+      <c r="G55" s="25"/>
       <c r="H55" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A56" s="7"/>
       <c r="B56" s="7"/>
       <c r="C56" s="8" t="s">
@@ -1962,12 +1995,12 @@
       <c r="F56" s="8">
         <v>5</v>
       </c>
-      <c r="G56" s="24"/>
+      <c r="G56" s="25"/>
       <c r="H56" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.2">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A57" s="7"/>
       <c r="B57" s="7"/>
       <c r="C57" s="8" t="s">
@@ -1978,12 +2011,12 @@
       <c r="F57" s="8">
         <v>10</v>
       </c>
-      <c r="G57" s="24"/>
+      <c r="G57" s="25"/>
       <c r="H57" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A58" s="7"/>
       <c r="B58" s="7"/>
       <c r="C58" s="8" t="s">
@@ -1994,12 +2027,12 @@
       <c r="F58" s="8">
         <v>5</v>
       </c>
-      <c r="G58" s="24"/>
+      <c r="G58" s="25"/>
       <c r="H58" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A59" s="7"/>
       <c r="B59" s="7" t="s">
         <v>77</v>
@@ -2012,9 +2045,9 @@
       <c r="F59" s="8">
         <v>5</v>
       </c>
-      <c r="G59" s="24"/>
-    </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="G59" s="25"/>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A60" s="7"/>
       <c r="B60" s="7"/>
       <c r="C60" s="8" t="s">
@@ -2025,9 +2058,9 @@
       <c r="F60" s="8">
         <v>20</v>
       </c>
-      <c r="G60" s="24"/>
-    </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="G60" s="25"/>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A61" s="7"/>
       <c r="B61" s="7"/>
       <c r="C61" s="8" t="s">
@@ -2038,9 +2071,9 @@
       <c r="F61" s="8">
         <v>10</v>
       </c>
-      <c r="G61" s="24"/>
-    </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="G61" s="25"/>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A62" s="7"/>
       <c r="B62" s="7"/>
       <c r="C62" s="8"/>
@@ -2052,9 +2085,9 @@
         <v>0</v>
       </c>
       <c r="F62" s="8"/>
-      <c r="G62" s="24"/>
-    </row>
-    <row r="63" spans="1:13" ht="19" x14ac:dyDescent="0.25">
+      <c r="G62" s="25"/>
+    </row>
+    <row r="63" spans="1:13" ht="18" x14ac:dyDescent="0.35">
       <c r="A63" s="1"/>
       <c r="E63">
         <f>SUM(E49:E62)</f>
@@ -2067,7 +2100,7 @@
       <c r="L63" s="5"/>
       <c r="M63" s="5"/>
     </row>
-    <row r="64" spans="1:13" s="5" customFormat="1" ht="19" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13" s="5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A64" s="5" t="s">
         <v>101</v>
       </c>
@@ -2075,7 +2108,7 @@
       <c r="K64"/>
       <c r="L64"/>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" s="7" t="str">
         <f>$A$64</f>
         <v>Montageanleitung</v>
@@ -2091,8 +2124,11 @@
       <c r="F65" s="8">
         <v>10</v>
       </c>
-    </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="G65" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" s="7"/>
       <c r="B66" s="7" t="s">
         <v>66</v>
@@ -2106,7 +2142,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" s="7"/>
       <c r="B67" s="7"/>
       <c r="C67" s="8" t="s">
@@ -2118,7 +2154,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" s="7"/>
       <c r="B68" s="7"/>
       <c r="C68" s="8" t="s">
@@ -2130,7 +2166,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" s="7"/>
       <c r="B69" s="7"/>
       <c r="C69" s="8" t="s">
@@ -2142,7 +2178,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" s="7"/>
       <c r="B70" s="7"/>
       <c r="C70" s="8" t="s">
@@ -2154,7 +2190,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" s="7"/>
       <c r="B71" s="7"/>
       <c r="C71" s="8" t="s">
@@ -2166,7 +2202,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" s="7"/>
       <c r="B72" s="7"/>
       <c r="C72" s="8"/>
@@ -2179,7 +2215,7 @@
       </c>
       <c r="F72" s="8"/>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="E73">
@@ -2191,17 +2227,17 @@
         <v>100</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" s="1"/>
     </row>
-    <row r="75" spans="1:12" s="5" customFormat="1" ht="19" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" s="5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A75" s="5" t="s">
         <v>107</v>
       </c>
       <c r="K75"/>
       <c r="L75"/>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" s="7" t="s">
         <v>107</v>
       </c>
@@ -2216,8 +2252,11 @@
       <c r="F76" s="8">
         <v>10</v>
       </c>
-    </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="G76" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77" s="7"/>
       <c r="B77" s="7" t="s">
         <v>66</v>
@@ -2231,7 +2270,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" s="7"/>
       <c r="B78" s="7"/>
       <c r="C78" s="8" t="s">
@@ -2243,7 +2282,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" s="7"/>
       <c r="B79" s="7"/>
       <c r="C79" s="8" t="s">
@@ -2255,7 +2294,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80" s="7"/>
       <c r="B80" s="7"/>
       <c r="C80" s="8" t="s">
@@ -2267,7 +2306,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" s="7"/>
       <c r="B81" s="7"/>
       <c r="C81" s="8" t="s">
@@ -2279,7 +2318,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" s="7"/>
       <c r="B82" s="7"/>
       <c r="C82" s="8" t="s">
@@ -2291,7 +2330,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" s="7"/>
       <c r="B83" s="7"/>
       <c r="C83" s="8"/>
@@ -2304,7 +2343,7 @@
       </c>
       <c r="F83" s="8"/>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="E84">
@@ -2316,15 +2355,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" s="1"/>
     </row>
-    <row r="86" spans="1:6" ht="19" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A86" s="5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" s="7" t="s">
         <v>34</v>
       </c>
@@ -2339,8 +2378,11 @@
       <c r="F87" s="8">
         <v>10</v>
       </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G87" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" s="7"/>
       <c r="B88" s="8"/>
       <c r="C88" s="8" t="s">
@@ -2352,7 +2394,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" s="7"/>
       <c r="B89" s="8"/>
       <c r="C89" s="8" t="s">
@@ -2364,7 +2406,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" s="7"/>
       <c r="B90" s="7" t="s">
         <v>66</v>
@@ -2378,7 +2420,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" s="7"/>
       <c r="B91" s="7"/>
       <c r="C91" s="8" t="s">
@@ -2390,7 +2432,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" s="7"/>
       <c r="B92" s="7"/>
       <c r="C92" s="8" t="s">
@@ -2402,7 +2444,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" s="7"/>
       <c r="B93" s="7"/>
       <c r="C93" s="8" t="s">
@@ -2414,7 +2456,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" s="7"/>
       <c r="B94" s="7"/>
       <c r="C94" s="7"/>
@@ -2427,7 +2469,7 @@
       </c>
       <c r="F94" s="7"/>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="E95">
@@ -2439,15 +2481,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" s="1"/>
     </row>
-    <row r="97" spans="1:6" ht="19" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A97" s="5" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" s="7" t="s">
         <v>61</v>
       </c>
@@ -2462,8 +2504,11 @@
       <c r="F98" s="8">
         <v>10</v>
       </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G98" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" s="7"/>
       <c r="B99" s="8"/>
       <c r="C99" s="8" t="s">
@@ -2475,7 +2520,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" s="7"/>
       <c r="B100" s="7" t="s">
         <v>66</v>
@@ -2489,7 +2534,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" s="7"/>
       <c r="B101" s="7"/>
       <c r="C101" s="8" t="s">
@@ -2501,7 +2546,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" s="7"/>
       <c r="B102" s="7"/>
       <c r="C102" s="7"/>
@@ -2514,7 +2559,7 @@
       </c>
       <c r="F102" s="7"/>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="E103">
@@ -2526,16 +2571,16 @@
         <v>50</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
     </row>
-    <row r="105" spans="1:6" ht="19" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A105" s="5" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" s="7" t="s">
         <v>152</v>
       </c>
@@ -2552,8 +2597,11 @@
       <c r="F106" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G106" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" s="7"/>
       <c r="B107" s="7" t="s">
         <v>66</v>
@@ -2567,7 +2615,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" s="7"/>
       <c r="B108" s="7"/>
       <c r="C108" s="8" t="s">
@@ -2579,7 +2627,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" s="7"/>
       <c r="B109" s="7"/>
       <c r="C109" s="8" t="s">
@@ -2591,7 +2639,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" s="7"/>
       <c r="B110" s="7"/>
       <c r="C110" s="7"/>
@@ -2604,7 +2652,7 @@
       </c>
       <c r="F110" s="7"/>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="E111">
@@ -2616,16 +2664,16 @@
         <v>50</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
     </row>
-    <row r="113" spans="1:6" ht="19" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A113" s="5" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" s="7" t="s">
         <v>156</v>
       </c>
@@ -2642,8 +2690,11 @@
       <c r="F114" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G114" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" s="7"/>
       <c r="B115" s="7" t="s">
         <v>66</v>
@@ -2657,7 +2708,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" s="7"/>
       <c r="B116" s="7"/>
       <c r="C116" s="8" t="s">
@@ -2669,7 +2720,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" s="7"/>
       <c r="B117" s="7"/>
       <c r="C117" s="8" t="s">
@@ -2681,7 +2732,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" s="7"/>
       <c r="B118" s="7"/>
       <c r="C118" s="7"/>
@@ -2694,7 +2745,7 @@
       </c>
       <c r="F118" s="7"/>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="E119">
@@ -2706,18 +2757,18 @@
         <v>50</v>
       </c>
     </row>
-    <row r="120" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="121" spans="1:6" ht="21" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="121" spans="1:7" ht="21" x14ac:dyDescent="0.4">
       <c r="A121" s="16" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="122" spans="1:6" ht="19" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A122" s="5" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" s="7" t="s">
         <v>117</v>
       </c>
@@ -2730,8 +2781,11 @@
       <c r="F123" s="8">
         <v>5</v>
       </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G123" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" s="8"/>
       <c r="B124" s="8"/>
       <c r="C124" s="8" t="s">
@@ -2745,7 +2799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" s="8"/>
       <c r="B125" s="8"/>
       <c r="C125" s="8" t="s">
@@ -2757,7 +2811,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" s="8"/>
       <c r="B126" s="8"/>
       <c r="C126" s="8" t="s">
@@ -2769,7 +2823,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" s="8"/>
       <c r="B127" s="8"/>
       <c r="C127" s="8" t="s">
@@ -2781,7 +2835,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" s="8"/>
       <c r="B128" s="8"/>
       <c r="C128" s="8" t="s">
@@ -2793,7 +2847,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" s="8"/>
       <c r="B129" s="8"/>
       <c r="C129" s="8"/>
@@ -2806,7 +2860,7 @@
       </c>
       <c r="F129" s="8"/>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E130">
         <f>SUM(E123:E129)</f>
         <v>0</v>
@@ -2816,12 +2870,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="131" spans="1:7" ht="19" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A131" s="5" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" s="7" t="s">
         <v>121</v>
       </c>
@@ -2835,7 +2889,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" s="7"/>
       <c r="B133" s="8" t="s">
         <v>124</v>
@@ -2847,7 +2901,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" s="8"/>
       <c r="B134" s="8" t="s">
         <v>125</v>
@@ -2859,7 +2913,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" s="8"/>
       <c r="B135" s="19"/>
       <c r="C135" s="8"/>
@@ -2872,7 +2926,7 @@
       </c>
       <c r="F135" s="8"/>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E136">
         <f>SUM(E132:E135)</f>
         <v>0</v>
@@ -2882,7 +2936,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" s="7" t="s">
         <v>126</v>
       </c>
@@ -2890,7 +2944,7 @@
         <v>91</v>
       </c>
       <c r="C139" s="8" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="D139" s="8"/>
       <c r="E139" s="8" t="s">
@@ -2900,11 +2954,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" s="8"/>
       <c r="B140" s="8"/>
       <c r="C140" s="8" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="D140" s="8"/>
       <c r="E140" s="8" t="s">
@@ -2913,11 +2967,11 @@
       <c r="F140" s="8">
         <v>10</v>
       </c>
-      <c r="G140" s="25" t="s">
+      <c r="G140" s="26" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" s="7" t="s">
         <v>127</v>
       </c>
@@ -2932,9 +2986,9 @@
       <c r="F141" s="8">
         <v>10</v>
       </c>
-      <c r="G141" s="25"/>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G141" s="26"/>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" s="8"/>
       <c r="B142" s="8"/>
       <c r="C142" s="8" t="s">
@@ -2947,9 +3001,9 @@
       <c r="F142" s="8">
         <v>10</v>
       </c>
-      <c r="G142" s="25"/>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G142" s="26"/>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" s="8"/>
       <c r="B143" s="8"/>
       <c r="C143" s="8" t="s">
@@ -2962,9 +3016,9 @@
       <c r="F143" s="8">
         <v>10</v>
       </c>
-      <c r="G143" s="25"/>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G143" s="26"/>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" s="7"/>
       <c r="B144" s="8"/>
       <c r="C144" s="8" t="s">
@@ -2977,9 +3031,9 @@
       <c r="F144" s="8">
         <v>50</v>
       </c>
-      <c r="G144" s="25"/>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G144" s="26"/>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145" s="8"/>
       <c r="B145" s="8"/>
       <c r="C145" s="8" t="s">
@@ -2994,9 +3048,9 @@
       <c r="F145" s="8">
         <v>30</v>
       </c>
-      <c r="G145" s="25"/>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G145" s="26"/>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146" s="7"/>
       <c r="B146" s="8"/>
       <c r="C146" s="8" t="s">
@@ -3009,9 +3063,9 @@
       <c r="F146" s="8">
         <v>40</v>
       </c>
-      <c r="G146" s="25"/>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G146" s="26"/>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" s="8"/>
       <c r="B147" s="8"/>
       <c r="C147" s="8"/>
@@ -3023,9 +3077,9 @@
         <v>0</v>
       </c>
       <c r="F147" s="8"/>
-      <c r="G147" s="25"/>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G147" s="26"/>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E148">
         <f>SUM(E144:E147)</f>
         <v>0</v>
@@ -3033,12 +3087,12 @@
       <c r="F148">
         <v>170</v>
       </c>
-      <c r="G148" s="25"/>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="G149" s="25"/>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G148" s="26"/>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G149" s="26"/>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150" s="7" t="s">
         <v>143</v>
       </c>
@@ -3053,9 +3107,9 @@
       <c r="F150" s="8">
         <v>10</v>
       </c>
-      <c r="G150" s="25"/>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G150" s="26"/>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A151" s="7" t="s">
         <v>134</v>
       </c>
@@ -3068,9 +3122,9 @@
       <c r="F151" s="8">
         <v>10</v>
       </c>
-      <c r="G151" s="25"/>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G151" s="26"/>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" s="7"/>
       <c r="B152" s="8"/>
       <c r="C152" s="8" t="s">
@@ -3081,9 +3135,9 @@
       <c r="F152" s="8">
         <v>10</v>
       </c>
-      <c r="G152" s="25"/>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G152" s="26"/>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153" s="7"/>
       <c r="B153" s="8"/>
       <c r="C153" s="8" t="s">
@@ -3096,9 +3150,9 @@
       <c r="F153" s="8">
         <v>10</v>
       </c>
-      <c r="G153" s="25"/>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G153" s="26"/>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A154" s="8"/>
       <c r="B154" s="8"/>
       <c r="C154" s="8" t="s">
@@ -3111,9 +3165,9 @@
       <c r="F154" s="8">
         <v>15</v>
       </c>
-      <c r="G154" s="25"/>
-    </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G154" s="26"/>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A155" s="8"/>
       <c r="B155" s="8"/>
       <c r="C155" s="8" t="s">
@@ -3126,9 +3180,9 @@
       <c r="F155" s="8">
         <v>10</v>
       </c>
-      <c r="G155" s="25"/>
-    </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G155" s="26"/>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A156" s="8"/>
       <c r="B156" s="8"/>
       <c r="C156" s="8" t="s">
@@ -3141,9 +3195,9 @@
       <c r="F156" s="8">
         <v>15</v>
       </c>
-      <c r="G156" s="25"/>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G156" s="26"/>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A157" s="8"/>
       <c r="B157" s="8"/>
       <c r="C157" s="8" t="s">
@@ -3154,9 +3208,9 @@
       <c r="F157" s="8">
         <v>15</v>
       </c>
-      <c r="G157" s="25"/>
-    </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G157" s="26"/>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158" s="8"/>
       <c r="B158" s="8"/>
       <c r="C158" s="8" t="s">
@@ -3167,9 +3221,9 @@
       <c r="F158" s="8">
         <v>5</v>
       </c>
-      <c r="G158" s="25"/>
-    </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G158" s="26"/>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159" s="8"/>
       <c r="B159" s="8"/>
       <c r="C159" s="8" t="s">
@@ -3182,9 +3236,9 @@
       <c r="F159" s="8">
         <v>0</v>
       </c>
-      <c r="G159" s="25"/>
-    </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G159" s="26"/>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A160" s="8"/>
       <c r="B160" s="8"/>
       <c r="C160" s="8"/>
@@ -3196,9 +3250,9 @@
         <v>0</v>
       </c>
       <c r="F160" s="8"/>
-      <c r="G160" s="25"/>
-    </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G160" s="26"/>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E161">
         <f>SUM(E150:E160)</f>
         <v>-100</v>
@@ -3207,12 +3261,12 @@
         <f>SUM(F150:F159)</f>
         <v>100</v>
       </c>
-      <c r="G161" s="25"/>
-    </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="G162" s="25"/>
-    </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G161" s="26"/>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G162" s="26"/>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A163" s="7" t="str">
         <f>A150</f>
         <v>Domänwissen Sensor/Aktor</v>
@@ -3230,9 +3284,9 @@
         <f t="shared" ref="F163:F171" si="1">F150</f>
         <v>10</v>
       </c>
-      <c r="G163" s="25"/>
-    </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G163" s="26"/>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A164" s="8" t="str">
         <f>$A$151</f>
         <v>z.B. Kamera, IMU, SPI</v>
@@ -3250,9 +3304,9 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="G164" s="25"/>
-    </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G164" s="26"/>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A165" s="8"/>
       <c r="B165" s="8"/>
       <c r="C165" s="8" t="str">
@@ -3267,9 +3321,9 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="G165" s="25"/>
-    </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G165" s="26"/>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A166" s="7"/>
       <c r="B166" s="8"/>
       <c r="C166" s="8" t="str">
@@ -3284,9 +3338,9 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="G166" s="25"/>
-    </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G166" s="26"/>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A167" s="7"/>
       <c r="B167" s="8"/>
       <c r="C167" s="8" t="str">
@@ -3301,9 +3355,9 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="G167" s="25"/>
-    </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G167" s="26"/>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A168" s="7"/>
       <c r="B168" s="8"/>
       <c r="C168" s="8" t="str">
@@ -3316,9 +3370,9 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="G168" s="25"/>
-    </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G168" s="26"/>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A169" s="7"/>
       <c r="B169" s="8"/>
       <c r="C169" s="8" t="str">
@@ -3333,9 +3387,9 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="G169" s="25"/>
-    </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G169" s="26"/>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A170" s="8"/>
       <c r="B170" s="8"/>
       <c r="C170" s="8" t="str">
@@ -3350,9 +3404,9 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="G170" s="25"/>
-    </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G170" s="26"/>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A171" s="8"/>
       <c r="B171" s="8"/>
       <c r="C171" s="8" t="str">
@@ -3365,9 +3419,9 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="G171" s="25"/>
-    </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G171" s="26"/>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A172" s="8"/>
       <c r="B172" s="8"/>
       <c r="C172" s="8" t="str">
@@ -3383,9 +3437,9 @@
         <f t="shared" ref="F172" si="3">F159</f>
         <v>0</v>
       </c>
-      <c r="G172" s="25"/>
-    </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G172" s="26"/>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A173" s="8"/>
       <c r="B173" s="8"/>
       <c r="C173" s="8"/>
@@ -3397,9 +3451,9 @@
         <v>0</v>
       </c>
       <c r="F173" s="8"/>
-      <c r="G173" s="25"/>
-    </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G173" s="26"/>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E174">
         <f>SUM(E163:E173)</f>
         <v>-100</v>
@@ -3408,9 +3462,9 @@
         <f>SUM(F163:F172)</f>
         <v>100</v>
       </c>
-      <c r="G174" s="25"/>
-    </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G174" s="26"/>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A175" s="7" t="str">
         <f>A163</f>
         <v>Domänwissen Sensor/Aktor</v>
@@ -3426,9 +3480,9 @@
         <f t="shared" ref="F175:F183" si="5">F163</f>
         <v>10</v>
       </c>
-      <c r="G175" s="25"/>
-    </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G175" s="26"/>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A176" s="7" t="str">
         <f>A164</f>
         <v>z.B. Kamera, IMU, SPI</v>
@@ -3444,9 +3498,9 @@
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="G176" s="25"/>
-    </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G176" s="26"/>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A177" s="7"/>
       <c r="B177" s="7"/>
       <c r="C177" s="8" t="str">
@@ -3459,9 +3513,9 @@
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="G177" s="25"/>
-    </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G177" s="26"/>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A178" s="7"/>
       <c r="B178" s="7"/>
       <c r="C178" s="8" t="str">
@@ -3474,9 +3528,9 @@
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="G178" s="25"/>
-    </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G178" s="26"/>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A179" s="7"/>
       <c r="B179" s="7"/>
       <c r="C179" s="8" t="str">
@@ -3489,9 +3543,9 @@
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
-      <c r="G179" s="25"/>
-    </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G179" s="26"/>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A180" s="7"/>
       <c r="B180" s="7"/>
       <c r="C180" s="8" t="str">
@@ -3504,9 +3558,9 @@
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="G180" s="25"/>
-    </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G180" s="26"/>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A181" s="7"/>
       <c r="B181" s="7"/>
       <c r="C181" s="8" t="str">
@@ -3519,9 +3573,9 @@
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
-      <c r="G181" s="25"/>
-    </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G181" s="26"/>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A182" s="7"/>
       <c r="B182" s="7"/>
       <c r="C182" s="8" t="str">
@@ -3534,9 +3588,9 @@
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
-      <c r="G182" s="25"/>
-    </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G182" s="26"/>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A183" s="7"/>
       <c r="B183" s="7"/>
       <c r="C183" s="8" t="str">
@@ -3549,9 +3603,9 @@
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="G183" s="25"/>
-    </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G183" s="26"/>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A184" s="7"/>
       <c r="B184" s="7"/>
       <c r="C184" s="8" t="str">
@@ -3567,9 +3621,9 @@
         <f t="shared" ref="F184" si="7">F172</f>
         <v>0</v>
       </c>
-      <c r="G184" s="25"/>
-    </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G184" s="26"/>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A185" s="7"/>
       <c r="B185" s="7"/>
       <c r="C185" s="8"/>
@@ -3581,9 +3635,9 @@
         <v>0</v>
       </c>
       <c r="F185" s="8"/>
-      <c r="G185" s="25"/>
-    </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G185" s="26"/>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="E186">
@@ -3594,9 +3648,9 @@
         <f>SUM(F175:F184)</f>
         <v>100</v>
       </c>
-      <c r="G186" s="25"/>
-    </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G186" s="26"/>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A187" s="7" t="s">
         <v>144</v>
       </c>
@@ -3611,9 +3665,9 @@
       <c r="F187" s="8">
         <v>10</v>
       </c>
-      <c r="G187" s="25"/>
-    </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G187" s="26"/>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A188" s="7"/>
       <c r="B188" s="8"/>
       <c r="C188" s="8" t="s">
@@ -3624,9 +3678,9 @@
       <c r="F188" s="8">
         <v>10</v>
       </c>
-      <c r="G188" s="25"/>
-    </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G188" s="26"/>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A189" s="7"/>
       <c r="B189" s="8"/>
       <c r="C189" s="8" t="s">
@@ -3637,9 +3691,9 @@
       <c r="F189" s="8">
         <v>10</v>
       </c>
-      <c r="G189" s="25"/>
-    </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G189" s="26"/>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A190" s="7"/>
       <c r="B190" s="8"/>
       <c r="C190" s="8" t="s">
@@ -3650,9 +3704,9 @@
       <c r="F190" s="8">
         <v>10</v>
       </c>
-      <c r="G190" s="25"/>
-    </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G190" s="26"/>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A191" s="7"/>
       <c r="B191" s="8"/>
       <c r="C191" s="8" t="s">
@@ -3663,9 +3717,9 @@
       <c r="F191" s="8">
         <v>10</v>
       </c>
-      <c r="G191" s="25"/>
-    </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G191" s="26"/>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A192" s="7"/>
       <c r="B192" s="8"/>
       <c r="C192" s="8" t="s">
@@ -3676,9 +3730,9 @@
       <c r="F192" s="8">
         <v>10</v>
       </c>
-      <c r="G192" s="25"/>
-    </row>
-    <row r="193" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="G192" s="26"/>
+    </row>
+    <row r="193" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A193" s="7"/>
       <c r="B193" s="8"/>
       <c r="C193" s="8" t="s">
@@ -3689,9 +3743,9 @@
       <c r="F193" s="8">
         <v>10</v>
       </c>
-      <c r="G193" s="25"/>
-    </row>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="G193" s="26"/>
+    </row>
+    <row r="194" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A194" s="7"/>
       <c r="B194" s="8"/>
       <c r="C194" s="8" t="s">
@@ -3706,13 +3760,13 @@
       <c r="F194" s="8">
         <v>10</v>
       </c>
-      <c r="G194" s="25"/>
-    </row>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="G194" s="26"/>
+    </row>
+    <row r="195" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A195" s="8"/>
       <c r="B195" s="8"/>
       <c r="C195" s="8" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="D195" s="8"/>
       <c r="E195" s="8" t="s">
@@ -3721,9 +3775,9 @@
       <c r="F195" s="8">
         <v>10</v>
       </c>
-      <c r="G195" s="25"/>
-    </row>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="G195" s="26"/>
+    </row>
+    <row r="196" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A196" s="8"/>
       <c r="B196" s="8"/>
       <c r="C196" s="8" t="s">
@@ -3736,9 +3790,9 @@
       <c r="F196" s="8">
         <v>5</v>
       </c>
-      <c r="G196" s="25"/>
-    </row>
-    <row r="197" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="G196" s="26"/>
+    </row>
+    <row r="197" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A197" s="8"/>
       <c r="B197" s="8"/>
       <c r="C197" s="8" t="s">
@@ -3751,9 +3805,9 @@
       <c r="F197" s="8">
         <v>5</v>
       </c>
-      <c r="G197" s="25"/>
-    </row>
-    <row r="198" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="G197" s="26"/>
+    </row>
+    <row r="198" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A198" s="8"/>
       <c r="B198" s="8"/>
       <c r="C198" s="8"/>
@@ -3765,9 +3819,9 @@
         <v>0</v>
       </c>
       <c r="F198" s="8"/>
-      <c r="G198" s="25"/>
-    </row>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="G198" s="26"/>
+    </row>
+    <row r="199" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E199">
         <f>SUM(E187:E198)</f>
         <v>0</v>
@@ -3776,22 +3830,22 @@
         <f>SUM(F187:F197)</f>
         <v>100</v>
       </c>
-      <c r="G199" s="25"/>
-    </row>
-    <row r="200" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="G200" s="25"/>
-    </row>
-    <row r="201" spans="1:12" s="5" customFormat="1" ht="19" x14ac:dyDescent="0.25">
+      <c r="G199" s="26"/>
+    </row>
+    <row r="200" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="G200" s="26"/>
+    </row>
+    <row r="201" spans="1:12" s="5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A201" s="5" t="s">
         <v>160</v>
       </c>
       <c r="K201"/>
       <c r="L201"/>
     </row>
-    <row r="202" spans="1:12" ht="19" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:12" ht="18" x14ac:dyDescent="0.35">
       <c r="A202" s="5"/>
     </row>
-    <row r="203" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A203" s="7" t="s">
         <v>161</v>
       </c>
@@ -3804,8 +3858,11 @@
       <c r="F203" s="8">
         <v>10</v>
       </c>
-    </row>
-    <row r="204" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="G203" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="204" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A204" s="8"/>
       <c r="B204" s="8"/>
       <c r="C204" s="8" t="s">
@@ -3817,7 +3874,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="205" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A205" s="8"/>
       <c r="B205" s="8"/>
       <c r="C205" s="8" t="s">
@@ -3829,7 +3886,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="206" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A206" s="8"/>
       <c r="B206" s="8"/>
       <c r="C206" s="8" t="s">
@@ -3841,7 +3898,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="207" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A207" s="8"/>
       <c r="B207" s="8"/>
       <c r="C207" s="8" t="s">
@@ -3853,7 +3910,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="208" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A208" s="8"/>
       <c r="B208" s="8"/>
       <c r="C208" s="8" t="s">
@@ -3865,7 +3922,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A209" s="8"/>
       <c r="B209" s="8"/>
       <c r="C209" s="8" t="s">
@@ -3877,7 +3934,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A210" s="8"/>
       <c r="B210" s="8"/>
       <c r="C210" s="8"/>
@@ -3890,7 +3947,7 @@
       </c>
       <c r="F210" s="8"/>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E211">
         <f>SUM(E203:E210)</f>
         <v>0</v>
@@ -3900,12 +3957,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="213" spans="1:7" ht="19" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A213" s="5" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.2">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A214" s="7" t="s">
         <v>167</v>
       </c>
@@ -3918,11 +3975,11 @@
       <c r="F214" s="8">
         <v>5</v>
       </c>
-      <c r="G214" s="26" t="s">
+      <c r="G214" s="27" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A215" s="7" t="s">
         <v>45</v>
       </c>
@@ -3935,9 +3992,9 @@
       <c r="F215" s="8">
         <v>10</v>
       </c>
-      <c r="G215" s="26"/>
-    </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G215" s="27"/>
+    </row>
+    <row r="216" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A216" s="7"/>
       <c r="B216" s="7"/>
       <c r="C216" s="8" t="s">
@@ -3948,9 +4005,9 @@
       <c r="F216" s="8">
         <v>10</v>
       </c>
-      <c r="G216" s="26"/>
-    </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G216" s="27"/>
+    </row>
+    <row r="217" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A217" s="7"/>
       <c r="B217" s="7"/>
       <c r="C217" s="8" t="s">
@@ -3961,9 +4018,9 @@
       <c r="F217" s="8">
         <v>5</v>
       </c>
-      <c r="G217" s="26"/>
-    </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G217" s="27"/>
+    </row>
+    <row r="218" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A218" s="7"/>
       <c r="B218" s="7"/>
       <c r="C218" s="8" t="s">
@@ -3974,9 +4031,9 @@
       <c r="F218" s="8">
         <v>5</v>
       </c>
-      <c r="G218" s="26"/>
-    </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G218" s="27"/>
+    </row>
+    <row r="219" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A219" s="7"/>
       <c r="B219" s="7"/>
       <c r="C219" s="8" t="s">
@@ -3987,9 +4044,9 @@
       <c r="F219" s="8">
         <v>5</v>
       </c>
-      <c r="G219" s="26"/>
-    </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G219" s="27"/>
+    </row>
+    <row r="220" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A220" s="7"/>
       <c r="B220" s="7"/>
       <c r="C220" s="8"/>
@@ -4001,9 +4058,9 @@
         <v>0</v>
       </c>
       <c r="F220" s="8"/>
-      <c r="G220" s="26"/>
-    </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G220" s="27"/>
+    </row>
+    <row r="221" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="E221">
@@ -4014,14 +4071,14 @@
         <f>SUM(F214:F219)</f>
         <v>40</v>
       </c>
-      <c r="G221" s="26"/>
-    </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G221" s="27"/>
+    </row>
+    <row r="222" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
-      <c r="G222" s="26"/>
-    </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G222" s="27"/>
+    </row>
+    <row r="223" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A223" s="7" t="s">
         <v>167</v>
       </c>
@@ -4034,9 +4091,9 @@
       <c r="F223" s="8">
         <v>5</v>
       </c>
-      <c r="G223" s="26"/>
-    </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G223" s="27"/>
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A224" s="7" t="s">
         <v>187</v>
       </c>
@@ -4049,9 +4106,9 @@
       <c r="F224" s="8">
         <v>25</v>
       </c>
-      <c r="G224" s="26"/>
-    </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G224" s="27"/>
+    </row>
+    <row r="225" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A225" s="7"/>
       <c r="B225" s="7"/>
       <c r="C225" s="8" t="s">
@@ -4062,9 +4119,9 @@
       <c r="F225" s="8">
         <v>15</v>
       </c>
-      <c r="G225" s="26"/>
-    </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G225" s="27"/>
+    </row>
+    <row r="226" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A226" s="7"/>
       <c r="B226" s="7"/>
       <c r="C226" s="8" t="s">
@@ -4075,9 +4132,9 @@
       <c r="F226" s="8">
         <v>15</v>
       </c>
-      <c r="G226" s="26"/>
-    </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G226" s="27"/>
+    </row>
+    <row r="227" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A227" s="7"/>
       <c r="B227" s="7"/>
       <c r="C227" s="8" t="s">
@@ -4088,9 +4145,9 @@
       <c r="F227" s="8">
         <v>20</v>
       </c>
-      <c r="G227" s="26"/>
-    </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G227" s="27"/>
+    </row>
+    <row r="228" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A228" s="7"/>
       <c r="B228" s="7"/>
       <c r="C228" s="8" t="s">
@@ -4101,9 +4158,9 @@
       <c r="F228" s="8">
         <v>15</v>
       </c>
-      <c r="G228" s="26"/>
-    </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G228" s="27"/>
+    </row>
+    <row r="229" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A229" s="7"/>
       <c r="B229" s="7"/>
       <c r="C229" s="8"/>
@@ -4115,9 +4172,9 @@
         <v>0</v>
       </c>
       <c r="F229" s="8"/>
-      <c r="G229" s="26"/>
-    </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G229" s="27"/>
+    </row>
+    <row r="230" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A230" s="1"/>
       <c r="B230" s="1"/>
       <c r="E230">
@@ -4128,14 +4185,14 @@
         <f>SUM(F223:F228)</f>
         <v>95</v>
       </c>
-      <c r="G230" s="26"/>
-    </row>
-    <row r="232" spans="1:7" ht="19" x14ac:dyDescent="0.25">
+      <c r="G230" s="27"/>
+    </row>
+    <row r="232" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A232" s="5" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.2">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A234" s="7" t="s">
         <v>170</v>
       </c>
@@ -4148,8 +4205,11 @@
       <c r="F234" s="8">
         <v>10</v>
       </c>
-    </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G234" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A235" s="7" t="s">
         <v>45</v>
       </c>
@@ -4163,7 +4223,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A236" s="7"/>
       <c r="B236" s="8" t="s">
         <v>172</v>
@@ -4175,7 +4235,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A237" s="7"/>
       <c r="B237" s="8" t="s">
         <v>173</v>
@@ -4187,7 +4247,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A238" s="7"/>
       <c r="B238" s="8" t="s">
         <v>87</v>
@@ -4199,7 +4259,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A239" s="7"/>
       <c r="B239" s="7" t="s">
         <v>174</v>
@@ -4213,7 +4273,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A240" s="7"/>
       <c r="B240" s="7"/>
       <c r="C240" s="8" t="s">
@@ -4225,7 +4285,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A241" s="7"/>
       <c r="B241" s="7"/>
       <c r="C241" s="8" t="s">
@@ -4237,7 +4297,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A242" s="7"/>
       <c r="B242" s="7"/>
       <c r="C242" s="8" t="s">
@@ -4249,7 +4309,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A243" s="7"/>
       <c r="B243" s="7"/>
       <c r="C243" s="8" t="s">
@@ -4261,7 +4321,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A244" s="7"/>
       <c r="B244" s="7"/>
       <c r="C244" s="8" t="s">
@@ -4273,7 +4333,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A245" s="7"/>
       <c r="B245" s="7"/>
       <c r="C245" s="8" t="s">
@@ -4287,7 +4347,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A246" s="7"/>
       <c r="B246" s="7"/>
       <c r="C246" s="8"/>
@@ -4299,7 +4359,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A247" s="7"/>
       <c r="B247" s="7"/>
       <c r="C247" s="8"/>
@@ -4311,7 +4371,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A248" s="7"/>
       <c r="B248" s="7"/>
       <c r="C248" s="8"/>
@@ -4323,7 +4383,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A249" s="7"/>
       <c r="B249" s="7"/>
       <c r="C249" s="8"/>
@@ -4335,7 +4395,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A250" s="7"/>
       <c r="B250" s="7"/>
       <c r="C250" s="8"/>
@@ -4348,7 +4408,7 @@
       </c>
       <c r="F250" s="8"/>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E251">
         <f>SUM(E234:E250)</f>
         <v>0</v>
@@ -4358,12 +4418,12 @@
         <v>150</v>
       </c>
     </row>
-    <row r="255" spans="1:6" ht="19" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A255" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A256" s="7" t="s">
         <v>170</v>
       </c>
@@ -4376,8 +4436,11 @@
       <c r="F256" s="8">
         <v>10</v>
       </c>
-    </row>
-    <row r="257" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="G256" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="257" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A257" s="7" t="s">
         <v>187</v>
       </c>
@@ -4391,7 +4454,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="258" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A258" s="7"/>
       <c r="B258" s="7"/>
       <c r="C258" s="8" t="s">
@@ -4403,7 +4466,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="259" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A259" s="7"/>
       <c r="B259" s="7"/>
       <c r="C259" s="8" t="s">
@@ -4415,7 +4478,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="260" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A260" s="7"/>
       <c r="B260" s="7"/>
       <c r="C260" s="8" t="s">
@@ -4427,7 +4490,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="261" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A261" s="7"/>
       <c r="B261" s="7" t="s">
         <v>174</v>
@@ -4441,7 +4504,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="262" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A262" s="7"/>
       <c r="B262" s="7"/>
       <c r="C262" s="8" t="s">
@@ -4453,7 +4516,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="263" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A263" s="7"/>
       <c r="B263" s="7"/>
       <c r="C263" s="8" t="s">
@@ -4465,7 +4528,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="264" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A264" s="7"/>
       <c r="B264" s="7"/>
       <c r="C264" s="8" t="s">
@@ -4477,7 +4540,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="265" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A265" s="7"/>
       <c r="B265" s="7"/>
       <c r="C265" s="8" t="s">
@@ -4489,7 +4552,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="266" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A266" s="7"/>
       <c r="B266" s="7"/>
       <c r="C266" s="8" t="s">
@@ -4503,7 +4566,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="267" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A267" s="7"/>
       <c r="B267" s="7"/>
       <c r="C267" s="8"/>
@@ -4515,7 +4578,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="268" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A268" s="7"/>
       <c r="B268" s="7"/>
       <c r="C268" s="8"/>
@@ -4527,7 +4590,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="269" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A269" s="7"/>
       <c r="B269" s="7"/>
       <c r="C269" s="8"/>
@@ -4539,7 +4602,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="270" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A270" s="7"/>
       <c r="B270" s="7"/>
       <c r="C270" s="8"/>
@@ -4551,7 +4614,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="271" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A271" s="8"/>
       <c r="B271" s="8"/>
       <c r="C271" s="8"/>
@@ -4564,7 +4627,7 @@
       </c>
       <c r="F271" s="8"/>
     </row>
-    <row r="272" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:12" ht="15" x14ac:dyDescent="0.3">
       <c r="E272">
         <f>SUM(E256:E271)</f>
         <v>0</v>
@@ -4576,7 +4639,7 @@
       <c r="K272" s="12"/>
       <c r="L272" s="12"/>
     </row>
-    <row r="273" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A273" s="7" t="s">
         <v>188</v>
       </c>
@@ -4591,8 +4654,11 @@
       <c r="F273" s="8">
         <v>10</v>
       </c>
-    </row>
-    <row r="274" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="G273" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="274" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A274" s="8"/>
       <c r="B274" s="8"/>
       <c r="C274" s="8" t="s">
@@ -4604,7 +4670,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="275" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A275" s="7"/>
       <c r="B275" s="8"/>
       <c r="C275" s="8" t="s">
@@ -4615,8 +4681,11 @@
       <c r="F275" s="8">
         <v>5</v>
       </c>
-    </row>
-    <row r="276" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="G275" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="276" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A276" s="8"/>
       <c r="B276" s="8"/>
       <c r="C276" s="8" t="s">
@@ -4629,8 +4698,11 @@
       <c r="F276" s="8">
         <v>5</v>
       </c>
-    </row>
-    <row r="277" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="G276" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="277" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A277" s="8"/>
       <c r="B277" s="8"/>
       <c r="C277" s="8" t="s">
@@ -4643,8 +4715,11 @@
       <c r="F277" s="8">
         <v>5</v>
       </c>
-    </row>
-    <row r="278" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="G277" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="278" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A278" s="7"/>
       <c r="B278" s="8"/>
       <c r="C278" s="8" t="s">
@@ -4658,7 +4733,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="279" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A279" s="7"/>
       <c r="B279" s="8"/>
       <c r="C279" s="8" t="s">
@@ -4672,7 +4747,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="280" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A280" s="8"/>
       <c r="B280" s="8"/>
       <c r="C280" s="8"/>
@@ -4685,7 +4760,7 @@
       </c>
       <c r="F280" s="8"/>
     </row>
-    <row r="281" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:12" ht="15" x14ac:dyDescent="0.3">
       <c r="E281">
         <f>SUM(E273:E280)</f>
         <v>0</v>
@@ -4697,22 +4772,22 @@
       <c r="K281" s="12"/>
       <c r="L281" s="12"/>
     </row>
-    <row r="282" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:12" ht="15" x14ac:dyDescent="0.3">
       <c r="K282" s="12"/>
       <c r="L282" s="12"/>
     </row>
-    <row r="283" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:12" ht="15" x14ac:dyDescent="0.3">
       <c r="K283" s="12"/>
       <c r="L283" s="12"/>
     </row>
-    <row r="285" spans="1:12" s="12" customFormat="1" ht="19" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:12" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A285" s="5" t="s">
         <v>196</v>
       </c>
       <c r="K285"/>
       <c r="L285"/>
     </row>
-    <row r="286" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A286" s="8" t="s">
         <v>197</v>
       </c>
@@ -4729,8 +4804,11 @@
       <c r="F286" s="8">
         <v>4</v>
       </c>
-    </row>
-    <row r="287" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="G286" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="287" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A287" s="8"/>
       <c r="B287" s="8"/>
       <c r="C287" s="8" t="s">
@@ -4744,7 +4822,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="288" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A288" s="8"/>
       <c r="B288" s="8"/>
       <c r="C288" s="8" t="s">
@@ -4758,7 +4836,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="289" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A289" s="8"/>
       <c r="B289" s="8"/>
       <c r="C289" s="8" t="s">
@@ -4772,7 +4850,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="290" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A290" s="8"/>
       <c r="B290" s="8"/>
       <c r="C290" s="8" t="s">
@@ -4786,7 +4864,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="291" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A291" s="8"/>
       <c r="B291" s="8"/>
       <c r="C291" s="8" t="s">
@@ -4800,7 +4878,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="292" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A292" s="8"/>
       <c r="B292" s="8"/>
       <c r="C292" s="8"/>
@@ -4813,7 +4891,7 @@
       </c>
       <c r="F292" s="8"/>
     </row>
-    <row r="293" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E293">
         <f>SUM(E286:E292)</f>
         <v>0</v>
@@ -4823,7 +4901,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="294" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A294" s="7" t="s">
         <v>1</v>
       </c>
@@ -4836,8 +4914,11 @@
       <c r="F294" s="8">
         <v>10</v>
       </c>
-    </row>
-    <row r="295" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="G294" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="295" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A295" s="7"/>
       <c r="B295" s="7"/>
       <c r="C295" s="21" t="s">
@@ -4849,7 +4930,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="296" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A296" s="7"/>
       <c r="B296" s="7"/>
       <c r="C296" s="21" t="s">
@@ -4861,7 +4942,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="297" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A297" s="7"/>
       <c r="B297" s="7"/>
       <c r="C297" s="8"/>
@@ -4869,7 +4950,7 @@
       <c r="E297" s="8"/>
       <c r="F297" s="8"/>
     </row>
-    <row r="298" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A298" s="7"/>
       <c r="B298" s="7"/>
       <c r="C298" s="8"/>
@@ -4882,7 +4963,7 @@
       </c>
       <c r="F298" s="8"/>
     </row>
-    <row r="299" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A299" s="1"/>
       <c r="B299" s="1"/>
       <c r="E299">
@@ -4895,12 +4976,12 @@
       </c>
       <c r="M299" s="14"/>
     </row>
-    <row r="302" spans="1:13" ht="19" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:13" ht="18" x14ac:dyDescent="0.35">
       <c r="A302" s="5" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="303" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A303" s="7" t="s">
         <v>202</v>
       </c>
@@ -4913,8 +4994,11 @@
       <c r="F303" s="8">
         <v>15</v>
       </c>
-    </row>
-    <row r="304" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="G303" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="304" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A304" s="7"/>
       <c r="B304" s="8" t="s">
         <v>203</v>
@@ -4926,7 +5010,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="305" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A305" s="7"/>
       <c r="B305" s="8" t="s">
         <v>204</v>
@@ -4938,7 +5022,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="306" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A306" s="7"/>
       <c r="B306" s="8" t="s">
         <v>205</v>
@@ -4952,7 +5036,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="307" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A307" s="7"/>
       <c r="B307" s="8"/>
       <c r="C307" s="8" t="s">
@@ -4964,7 +5048,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="308" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A308" s="7"/>
       <c r="B308" s="8" t="s">
         <v>104</v>
@@ -4978,7 +5062,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="309" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A309" s="7"/>
       <c r="B309" s="8"/>
       <c r="C309" s="8" t="s">
@@ -4990,7 +5074,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="310" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A310" s="7"/>
       <c r="B310" s="8"/>
       <c r="C310" s="8" t="s">
@@ -5002,7 +5086,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="311" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A311" s="7"/>
       <c r="B311" s="8"/>
       <c r="C311" s="8" t="s">
@@ -5014,7 +5098,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="312" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A312" s="7"/>
       <c r="B312" s="8"/>
       <c r="C312" s="8" t="s">
@@ -5026,7 +5110,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="313" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A313" s="7"/>
       <c r="B313" s="8"/>
       <c r="C313" s="8"/>
@@ -5039,7 +5123,7 @@
       </c>
       <c r="F313" s="8"/>
     </row>
-    <row r="314" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A314" s="1"/>
       <c r="E314">
         <f>SUM(E303:E313)</f>
@@ -5050,10 +5134,10 @@
         <v>105</v>
       </c>
     </row>
-    <row r="315" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A315" s="1"/>
     </row>
-    <row r="316" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A316" s="7" t="s">
         <v>211</v>
       </c>
@@ -5066,11 +5150,11 @@
       <c r="F316" s="8">
         <v>100</v>
       </c>
-      <c r="H316" s="27" t="s">
+      <c r="H316" s="28" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="317" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A317" s="8"/>
       <c r="B317" s="8" t="s">
         <v>213</v>
@@ -5081,9 +5165,9 @@
       <c r="F317" s="8">
         <v>100</v>
       </c>
-      <c r="H317" s="27"/>
-    </row>
-    <row r="318" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H317" s="28"/>
+    </row>
+    <row r="318" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A318" s="8"/>
       <c r="B318" s="8" t="s">
         <v>214</v>
@@ -5094,9 +5178,9 @@
       <c r="F318" s="8">
         <v>100</v>
       </c>
-      <c r="H318" s="27"/>
-    </row>
-    <row r="319" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H318" s="28"/>
+    </row>
+    <row r="319" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A319" s="8"/>
       <c r="B319" s="8" t="s">
         <v>215</v>
@@ -5107,9 +5191,9 @@
       <c r="F319" s="8">
         <v>100</v>
       </c>
-      <c r="H319" s="27"/>
-    </row>
-    <row r="320" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H319" s="28"/>
+    </row>
+    <row r="320" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A320" s="7" t="s">
         <v>216</v>
       </c>
@@ -5118,9 +5202,9 @@
       <c r="D320" s="8"/>
       <c r="E320" s="8"/>
       <c r="F320" s="8"/>
-      <c r="H320" s="27"/>
-    </row>
-    <row r="321" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H320" s="28"/>
+    </row>
+    <row r="321" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A321" s="7"/>
       <c r="B321" s="8" t="s">
         <v>217</v>
@@ -5131,9 +5215,9 @@
       <c r="F321" s="8">
         <v>50</v>
       </c>
-      <c r="H321" s="27"/>
-    </row>
-    <row r="322" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H321" s="28"/>
+    </row>
+    <row r="322" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A322" s="8"/>
       <c r="B322" s="8" t="s">
         <v>218</v>
@@ -5146,9 +5230,9 @@
       <c r="F322" s="8">
         <v>0</v>
       </c>
-      <c r="H322" s="27"/>
-    </row>
-    <row r="323" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H322" s="28"/>
+    </row>
+    <row r="323" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A323" s="8"/>
       <c r="B323" s="8" t="s">
         <v>219</v>
@@ -5161,9 +5245,9 @@
       <c r="F323" s="8">
         <v>0</v>
       </c>
-      <c r="H323" s="27"/>
-    </row>
-    <row r="324" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H323" s="28"/>
+    </row>
+    <row r="324" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A324" s="8"/>
       <c r="B324" s="8" t="s">
         <v>220</v>
@@ -5176,18 +5260,18 @@
       <c r="F324" s="8">
         <v>100</v>
       </c>
-      <c r="H324" s="27"/>
-    </row>
-    <row r="325" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H324" s="28"/>
+    </row>
+    <row r="325" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A325" s="8"/>
       <c r="B325" s="8"/>
       <c r="C325" s="8"/>
       <c r="D325" s="8"/>
       <c r="E325" s="8"/>
       <c r="F325" s="8"/>
-      <c r="H325" s="27"/>
-    </row>
-    <row r="326" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H325" s="28"/>
+    </row>
+    <row r="326" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A326" s="8"/>
       <c r="B326" s="8"/>
       <c r="C326" s="8"/>
@@ -5199,9 +5283,9 @@
         <v>0</v>
       </c>
       <c r="F326" s="8"/>
-      <c r="H326" s="27"/>
-    </row>
-    <row r="327" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H326" s="28"/>
+    </row>
+    <row r="327" spans="1:8" x14ac:dyDescent="0.3">
       <c r="E327">
         <f>SUM(E316:E326)</f>
         <v>-900</v>
@@ -5210,14 +5294,14 @@
         <f>SUM(F316:F325)</f>
         <v>550</v>
       </c>
-      <c r="H327" s="27"/>
-    </row>
-    <row r="328" spans="1:8" ht="19" x14ac:dyDescent="0.25">
+      <c r="H327" s="28"/>
+    </row>
+    <row r="328" spans="1:8" ht="18" x14ac:dyDescent="0.35">
       <c r="A328" s="5" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="329" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A329" s="8" t="s">
         <v>59</v>
       </c>
@@ -5232,8 +5316,11 @@
       <c r="F329" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="330" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G329" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="330" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A330" s="8"/>
       <c r="B330" s="8" t="s">
         <v>112</v>
@@ -5247,7 +5334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="331" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A331" s="8"/>
       <c r="B331" s="8" t="s">
         <v>104</v>
@@ -5259,7 +5346,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="332" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A332" s="8"/>
       <c r="B332" s="8" t="s">
         <v>221</v>
@@ -5273,7 +5360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A333" s="8"/>
       <c r="B333" s="8" t="s">
         <v>222</v>
@@ -5285,7 +5372,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="334" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A334" s="8"/>
       <c r="B334" s="8" t="s">
         <v>225</v>
@@ -5299,7 +5386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="335" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A335" s="8"/>
       <c r="B335" s="8" t="s">
         <v>224</v>
@@ -5311,7 +5398,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="336" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A336" s="8"/>
       <c r="B336" s="8" t="s">
         <v>223</v>
@@ -5323,7 +5410,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="337" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A337" s="8"/>
       <c r="B337" s="8"/>
       <c r="C337" s="8"/>
@@ -5336,7 +5423,7 @@
       </c>
       <c r="F337" s="8"/>
     </row>
-    <row r="338" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E338">
         <f>SUM(E329:E337)</f>
         <v>-200</v>
@@ -5346,7 +5433,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="340" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A340" s="8" t="s">
         <v>11</v>
       </c>
@@ -5362,7 +5449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="341" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A341" s="8"/>
       <c r="B341" s="8" t="s">
         <v>58</v>
@@ -5376,7 +5463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="342" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A342" s="8"/>
       <c r="B342" s="8" t="s">
         <v>56</v>
@@ -5390,7 +5477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A343" s="8"/>
       <c r="B343" s="8" t="s">
         <v>41</v>
@@ -5404,7 +5491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A344" s="8"/>
       <c r="B344" s="8"/>
       <c r="C344" s="8"/>
@@ -5419,7 +5506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="345" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E345">
         <f>SUM(E340:E344)</f>
         <v>-200</v>
@@ -5429,7 +5516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="346" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A346" s="7" t="s">
         <v>65</v>
       </c>
@@ -5447,7 +5534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="347" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A347" s="7"/>
       <c r="B347" s="7"/>
       <c r="C347" s="8"/>
@@ -5461,7 +5548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A348" s="7"/>
       <c r="B348" s="7"/>
       <c r="C348" s="8"/>
@@ -5475,7 +5562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="349" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A349" s="7"/>
       <c r="B349" s="7"/>
       <c r="C349" s="8" t="s">
@@ -5491,7 +5578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="350" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A350" s="7"/>
       <c r="B350" s="7"/>
       <c r="C350" s="8" t="s">
@@ -5507,7 +5594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="351" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A351" s="7"/>
       <c r="B351" s="7"/>
       <c r="C351" s="8"/>
@@ -5521,7 +5608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="352" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A352" s="7"/>
       <c r="B352" s="7"/>
       <c r="C352" s="8"/>
@@ -5535,7 +5622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="353" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A353" s="7"/>
       <c r="B353" s="7"/>
       <c r="C353" s="8"/>
@@ -5549,7 +5636,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="354" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E354">
         <f>SUM(E346:E353)</f>
         <v>-140</v>
@@ -5559,12 +5646,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="355" spans="1:6" ht="19" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A355" s="5" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="356" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A356" s="7" t="s">
         <v>90</v>
       </c>
@@ -5579,8 +5666,11 @@
       <c r="F356" s="8">
         <v>10</v>
       </c>
-    </row>
-    <row r="357" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G356" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="357" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A357" s="7"/>
       <c r="B357" s="8"/>
       <c r="C357" s="8" t="s">
@@ -5592,7 +5682,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="358" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A358" s="8"/>
       <c r="B358" s="7" t="s">
         <v>66</v>
@@ -5606,7 +5696,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="359" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A359" s="8"/>
       <c r="B359" s="8"/>
       <c r="C359" s="8" t="s">
@@ -5618,7 +5708,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="360" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A360" s="8"/>
       <c r="B360" s="8"/>
       <c r="C360" s="8" t="s">
@@ -5630,7 +5720,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="361" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A361" s="8"/>
       <c r="B361" s="8"/>
       <c r="C361" s="8" t="s">
@@ -5642,7 +5732,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="362" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A362" s="8"/>
       <c r="B362" s="8"/>
       <c r="C362" s="8" t="s">
@@ -5654,7 +5744,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="363" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A363" s="8"/>
       <c r="B363" s="8"/>
       <c r="C363" s="8"/>
@@ -5666,7 +5756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="364" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E364">
         <f>SUM(E356:E363)</f>
         <v>0</v>
@@ -5676,12 +5766,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="365" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A365" s="1" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="366" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A366" s="7" t="s">
         <v>242</v>
       </c>
@@ -5697,7 +5787,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="367" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A367" s="7" t="s">
         <v>243</v>
       </c>
@@ -5715,7 +5805,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="368" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A368" s="7"/>
       <c r="B368" s="8"/>
       <c r="C368" s="8" t="s">
@@ -5729,7 +5819,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="369" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A369" s="7"/>
       <c r="B369" s="8"/>
       <c r="C369" s="8"/>
@@ -5742,7 +5832,7 @@
       </c>
       <c r="F369" s="8"/>
     </row>
-    <row r="370" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E370">
         <f>SUM(E366:E369)</f>
         <v>0</v>
@@ -5752,12 +5842,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="372" spans="1:6" ht="19" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A372" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="373" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A373" s="7" t="s">
         <v>46</v>
       </c>
@@ -5771,7 +5861,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="374" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A374" s="7"/>
       <c r="B374" s="7" t="s">
         <v>48</v>
@@ -5783,7 +5873,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="375" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A375" s="7"/>
       <c r="B375" s="7" t="s">
         <v>49</v>
@@ -5795,7 +5885,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="376" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A376" s="7"/>
       <c r="B376" s="7" t="s">
         <v>50</v>
@@ -5807,7 +5897,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="377" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A377" s="7"/>
       <c r="B377" s="7" t="s">
         <v>51</v>
@@ -5819,7 +5909,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="378" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A378" s="7"/>
       <c r="B378" s="7" t="s">
         <v>52</v>
@@ -5831,7 +5921,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="379" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A379" s="7"/>
       <c r="B379" s="7" t="s">
         <v>53</v>
@@ -5843,7 +5933,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="380" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A380" s="7"/>
       <c r="B380" s="7" t="s">
         <v>54</v>
@@ -5855,7 +5945,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="381" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A381" s="7"/>
       <c r="B381" s="7"/>
       <c r="C381" s="8"/>
@@ -5868,7 +5958,7 @@
       </c>
       <c r="F381" s="8"/>
     </row>
-    <row r="382" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A382" s="1"/>
       <c r="B382" s="1"/>
       <c r="E382">
@@ -5880,10 +5970,10 @@
         <v>400</v>
       </c>
     </row>
-    <row r="387" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A387" s="7"/>
       <c r="B387" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="E387">
         <f>E382+E370+E364+E354+E345+E338+E327+E314+E299+E293+E281+E272+E251+E230+E221+E211+E199+E186+E174+E161+E148+E136+E130+E119+E111+E103+E95+E84+E73+E63+E46</f>
@@ -5898,65 +5988,65 @@
         <v>-0.57410296411856476</v>
       </c>
     </row>
-    <row r="388" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A388" s="9"/>
       <c r="B388" t="s">
-        <v>246</v>
+        <v>284</v>
       </c>
       <c r="H388" s="13">
         <f>(E388+E387)/(F388+F387)</f>
         <v>-0.57410296411856476</v>
       </c>
     </row>
-    <row r="389" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A389" s="10"/>
       <c r="B389" t="s">
-        <v>247</v>
+        <v>285</v>
       </c>
       <c r="H389" s="13">
         <f>(E389+E387)/(F389+F387)</f>
         <v>-0.57410296411856476</v>
       </c>
     </row>
-    <row r="390" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A390" s="11"/>
       <c r="B390" t="s">
-        <v>248</v>
+        <v>286</v>
       </c>
       <c r="H390" s="13">
         <f>(E390+E387)/(F390+F387)</f>
         <v>-0.57410296411856476</v>
       </c>
     </row>
-    <row r="391" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A391" s="20"/>
       <c r="B391" t="s">
-        <v>249</v>
+        <v>287</v>
       </c>
       <c r="H391" s="13">
         <f>(E391+E387)/(F391+F387)</f>
         <v>-0.57410296411856476</v>
       </c>
     </row>
-    <row r="392" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A392" s="22"/>
       <c r="B392" t="s">
-        <v>250</v>
+        <v>288</v>
       </c>
       <c r="H392" s="13">
         <f>(E392+E387)/(F392+F387)</f>
         <v>-0.57410296411856476</v>
       </c>
     </row>
-    <row r="394" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:8" x14ac:dyDescent="0.3">
       <c r="F394" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="G394" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="395" spans="1:8" x14ac:dyDescent="0.2">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="395" spans="1:8" x14ac:dyDescent="0.3">
       <c r="D395" t="s">
         <v>80</v>
       </c>
@@ -5964,7 +6054,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="396" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:8" x14ac:dyDescent="0.3">
       <c r="F396" s="18">
         <v>0.45</v>
       </c>
@@ -5972,7 +6062,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="397" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:8" x14ac:dyDescent="0.3">
       <c r="F397" s="18">
         <f>F396+(F405-F396)/9</f>
         <v>0.5</v>
@@ -5981,7 +6071,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="398" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:8" x14ac:dyDescent="0.3">
       <c r="F398" s="18">
         <f>F397+(F405-F396)/9</f>
         <v>0.55000000000000004</v>
@@ -5990,7 +6080,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="399" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:8" x14ac:dyDescent="0.3">
       <c r="F399" s="18">
         <f>F398+(F405-F396)/9</f>
         <v>0.60000000000000009</v>
@@ -5999,7 +6089,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="400" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:8" x14ac:dyDescent="0.3">
       <c r="F400" s="18">
         <f>F399+(F405-F396)/9</f>
         <v>0.65000000000000013</v>
@@ -6008,7 +6098,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="401" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="401" spans="5:7" x14ac:dyDescent="0.3">
       <c r="F401" s="18">
         <f>F400+(F405-F396)/9</f>
         <v>0.70000000000000018</v>
@@ -6017,7 +6107,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="402" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="402" spans="5:7" x14ac:dyDescent="0.3">
       <c r="F402" s="18">
         <f>F401+(F405-F396)/9</f>
         <v>0.75000000000000022</v>
@@ -6026,7 +6116,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="403" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="403" spans="5:7" x14ac:dyDescent="0.3">
       <c r="F403" s="18">
         <f>F402+(F405-F396)/9</f>
         <v>0.80000000000000027</v>
@@ -6035,7 +6125,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="404" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="404" spans="5:7" x14ac:dyDescent="0.3">
       <c r="F404" s="18">
         <f>F403+(F405-F396)/9</f>
         <v>0.85000000000000031</v>
@@ -6044,7 +6134,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="405" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="405" spans="5:7" x14ac:dyDescent="0.3">
       <c r="F405" s="18">
         <v>0.9</v>
       </c>
@@ -6052,9 +6142,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="406" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="406" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E406" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
     </row>
   </sheetData>
@@ -6079,33 +6169,33 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D37"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="35.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5" style="14"/>
+    <col min="2" max="2" width="35.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+    <row r="1" spans="1:4" ht="25.8" x14ac:dyDescent="0.5">
+      <c r="A1" s="29" t="s">
         <v>100</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="D4" s="14">
         <v>-1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>0</v>
       </c>
@@ -6113,111 +6203,111 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="D6" s="14">
         <v>-0.5</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="D7" s="14">
         <v>-0.5</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="D8" s="14">
         <v>-1</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="D9" s="14">
         <v>-1</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="D10" s="14">
         <v>-0.5</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="D11" s="14">
         <v>-0.5</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="D12" s="14">
         <v>-0.5</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="D13" s="14">
         <v>-0.5</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="D14" s="14">
         <v>-1</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="D15" s="14">
         <v>-0.3</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="D16" s="14">
         <v>-1</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="D17" s="14">
         <v>-0.2</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="D18" s="14">
         <v>-1</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>0</v>
       </c>
@@ -6231,7 +6321,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C23" t="s">
         <v>14</v>
       </c>
@@ -6239,7 +6329,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C24" t="s">
         <v>15</v>
       </c>
@@ -6247,7 +6337,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>16</v>
       </c>
@@ -6258,7 +6348,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C26" t="s">
         <v>18</v>
       </c>
@@ -6266,7 +6356,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C27" t="s">
         <v>19</v>
       </c>
@@ -6274,7 +6364,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C28" t="s">
         <v>20</v>
       </c>
@@ -6282,12 +6372,12 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
         <v>22</v>
       </c>
@@ -6298,7 +6388,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C32" t="s">
         <v>24</v>
       </c>
@@ -6306,7 +6396,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C33" t="s">
         <v>19</v>
       </c>
@@ -6314,7 +6404,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
         <v>30</v>
       </c>
@@ -6322,7 +6412,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
         <v>25</v>
       </c>
@@ -6333,7 +6423,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C36" t="s">
         <v>27</v>
       </c>
@@ -6341,7 +6431,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C37" t="s">
         <v>28</v>
       </c>
